--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/110.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/110.xlsx
@@ -426,13 +426,13 @@
         <v>-12.75362904390152</v>
       </c>
       <c r="E2">
-        <v>-15.21974131213889</v>
+        <v>-19.54785298733987</v>
       </c>
       <c r="F2">
-        <v>-5.452349321027077</v>
+        <v>-5.761049237329322</v>
       </c>
       <c r="G2">
-        <v>-18.38962476603536</v>
+        <v>-19.05968249372939</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.01921195340121</v>
       </c>
       <c r="E3">
-        <v>-16.40047298252882</v>
+        <v>-18.97934836041694</v>
       </c>
       <c r="F3">
-        <v>-5.703327115976343</v>
+        <v>-6.340729946145792</v>
       </c>
       <c r="G3">
-        <v>-17.75279829446454</v>
+        <v>-19.21192786198939</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.28708643730433</v>
       </c>
       <c r="E4">
-        <v>-17.48857471709185</v>
+        <v>-20.04030189330399</v>
       </c>
       <c r="F4">
-        <v>-5.298399644546081</v>
+        <v>-5.818391269262596</v>
       </c>
       <c r="G4">
-        <v>-17.77514613212739</v>
+        <v>-19.08075246081408</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.6408629146336</v>
       </c>
       <c r="E5">
-        <v>-16.08861056304259</v>
+        <v>-20.1928661826224</v>
       </c>
       <c r="F5">
-        <v>-5.13552024226088</v>
+        <v>-5.069655496943669</v>
       </c>
       <c r="G5">
-        <v>-18.54983365159008</v>
+        <v>-19.07780938582967</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.02821667847099</v>
       </c>
       <c r="E6">
-        <v>-17.33872751217804</v>
+        <v>-21.62777204211485</v>
       </c>
       <c r="F6">
-        <v>-5.21939093198368</v>
+        <v>-5.424502228062948</v>
       </c>
       <c r="G6">
-        <v>-18.17294459467175</v>
+        <v>-20.42644121961749</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.437362300293378</v>
       </c>
       <c r="E7">
-        <v>-17.9547720592335</v>
+        <v>-22.72260761752729</v>
       </c>
       <c r="F7">
-        <v>-5.074430370278719</v>
+        <v>-5.642314053731081</v>
       </c>
       <c r="G7">
-        <v>-18.47949117997165</v>
+        <v>-19.49993704754213</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.825602119302188</v>
       </c>
       <c r="E8">
-        <v>-19.96619341616846</v>
+        <v>-22.95024494894487</v>
       </c>
       <c r="F8">
-        <v>-4.791776081461791</v>
+        <v>-4.970061774892387</v>
       </c>
       <c r="G8">
-        <v>-17.77531000413158</v>
+        <v>-18.86871367429653</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.177534640058806</v>
       </c>
       <c r="E9">
-        <v>-21.07612239544846</v>
+        <v>-23.14631428805497</v>
       </c>
       <c r="F9">
-        <v>-4.50457338925572</v>
+        <v>-4.872389088116532</v>
       </c>
       <c r="G9">
-        <v>-17.33315188663375</v>
+        <v>-18.036526944635</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.478149847400849</v>
       </c>
       <c r="E10">
-        <v>-22.21083118449844</v>
+        <v>-23.58698009374137</v>
       </c>
       <c r="F10">
-        <v>-5.269194523759463</v>
+        <v>-5.038051853548118</v>
       </c>
       <c r="G10">
-        <v>-17.57631311176599</v>
+        <v>-18.06531875919005</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.731982488742514</v>
       </c>
       <c r="E11">
-        <v>-21.6769195705201</v>
+        <v>-24.11929315639501</v>
       </c>
       <c r="F11">
-        <v>-4.195791120245872</v>
+        <v>-5.322545616785829</v>
       </c>
       <c r="G11">
-        <v>-17.49157804341557</v>
+        <v>-18.43101155109456</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.962624345568536</v>
       </c>
       <c r="E12">
-        <v>-21.05136522804853</v>
+        <v>-24.18283217519663</v>
       </c>
       <c r="F12">
-        <v>-4.673645873523247</v>
+        <v>-4.634472907704852</v>
       </c>
       <c r="G12">
-        <v>-17.38747959420596</v>
+        <v>-18.20881104504421</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.193812050846315</v>
       </c>
       <c r="E13">
-        <v>-21.68135294657361</v>
+        <v>-26.09223606968679</v>
       </c>
       <c r="F13">
-        <v>-4.07574700370852</v>
+        <v>-4.741361971055607</v>
       </c>
       <c r="G13">
-        <v>-16.93117551561883</v>
+        <v>-19.43232743126637</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.466741542942899</v>
       </c>
       <c r="E14">
-        <v>-22.55654847566602</v>
+        <v>-25.32212830841638</v>
       </c>
       <c r="F14">
-        <v>-3.625576221685983</v>
+        <v>-5.064785601253694</v>
       </c>
       <c r="G14">
-        <v>-16.19118416868046</v>
+        <v>-17.74324074949266</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.810541863130946</v>
       </c>
       <c r="E15">
-        <v>-22.62060826897853</v>
+        <v>-28.70094050586343</v>
       </c>
       <c r="F15">
-        <v>-4.075100059842062</v>
+        <v>-4.269633784112109</v>
       </c>
       <c r="G15">
-        <v>-16.0210453017807</v>
+        <v>-17.010832207112</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.252657724342348</v>
       </c>
       <c r="E16">
-        <v>-24.08957730995667</v>
+        <v>-28.48177594931421</v>
       </c>
       <c r="F16">
-        <v>-3.290709524395889</v>
+        <v>-3.979784719321339</v>
       </c>
       <c r="G16">
-        <v>-16.05254183204132</v>
+        <v>-16.96912760968103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.812757899741952</v>
       </c>
       <c r="E17">
-        <v>-24.05857990537417</v>
+        <v>-29.66296952405292</v>
       </c>
       <c r="F17">
-        <v>-3.885941433449017</v>
+        <v>-3.86950810901746</v>
       </c>
       <c r="G17">
-        <v>-15.45756396663243</v>
+        <v>-15.78226227312415</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.497843943966642</v>
       </c>
       <c r="E18">
-        <v>-25.52408466373645</v>
+        <v>-28.92161304425721</v>
       </c>
       <c r="F18">
-        <v>-3.574485868853907</v>
+        <v>-4.098888114544921</v>
       </c>
       <c r="G18">
-        <v>-14.49981321048466</v>
+        <v>-15.42240266245983</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.312520783279294</v>
       </c>
       <c r="E19">
-        <v>-26.48113688899151</v>
+        <v>-29.36302604815488</v>
       </c>
       <c r="F19">
-        <v>-3.1324933441787</v>
+        <v>-3.387994203222461</v>
       </c>
       <c r="G19">
-        <v>-13.74064552851007</v>
+        <v>-16.92552275911052</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.247903928173035</v>
       </c>
       <c r="E20">
-        <v>-27.39136016453325</v>
+        <v>-31.34186503460464</v>
       </c>
       <c r="F20">
-        <v>-2.863913449832282</v>
+        <v>-3.595190448139404</v>
       </c>
       <c r="G20">
-        <v>-13.6607157170099</v>
+        <v>-15.54788723585313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.293839205811237</v>
       </c>
       <c r="E21">
-        <v>-27.27522744860655</v>
+        <v>-31.49412138769054</v>
       </c>
       <c r="F21">
-        <v>-2.892508843841456</v>
+        <v>-3.518204128031019</v>
       </c>
       <c r="G21">
-        <v>-13.33075695365628</v>
+        <v>-16.08233343134923</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.4309090001035</v>
       </c>
       <c r="E22">
-        <v>-27.90404682083765</v>
+        <v>-30.32712457896587</v>
       </c>
       <c r="F22">
-        <v>-2.874171113046583</v>
+        <v>-2.797293276793406</v>
       </c>
       <c r="G22">
-        <v>-13.4707632350576</v>
+        <v>-15.04300421202273</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.637118489930881</v>
       </c>
       <c r="E23">
-        <v>-27.71573928617669</v>
+        <v>-33.59627977831719</v>
       </c>
       <c r="F23">
-        <v>-2.19130246160374</v>
+        <v>-2.579551134185551</v>
       </c>
       <c r="G23">
-        <v>-13.53321336611041</v>
+        <v>-15.97490457332711</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.89004471183159</v>
       </c>
       <c r="E24">
-        <v>-28.3583206909171</v>
+        <v>-32.52021699190355</v>
       </c>
       <c r="F24">
-        <v>-2.335342098318873</v>
+        <v>-2.626997379706202</v>
       </c>
       <c r="G24">
-        <v>-14.36140923312435</v>
+        <v>-15.1147569760409</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.166415598695742</v>
       </c>
       <c r="E25">
-        <v>-28.5791879536932</v>
+        <v>-33.28600232473364</v>
       </c>
       <c r="F25">
-        <v>-2.45756222678404</v>
+        <v>-2.414684972829432</v>
       </c>
       <c r="G25">
-        <v>-12.86854520655432</v>
+        <v>-15.62892608010895</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.44684316685804</v>
       </c>
       <c r="E26">
-        <v>-29.44343816110908</v>
+        <v>-32.8286083360629</v>
       </c>
       <c r="F26">
-        <v>-1.992960716460019</v>
+        <v>-2.438821442833687</v>
       </c>
       <c r="G26">
-        <v>-13.62358794878698</v>
+        <v>-16.13450597377537</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.710262102192847</v>
       </c>
       <c r="E27">
-        <v>-28.85984465879258</v>
+        <v>-31.62762532991067</v>
       </c>
       <c r="F27">
-        <v>-1.921399380964973</v>
+        <v>-2.657687224788545</v>
       </c>
       <c r="G27">
-        <v>-13.81016698483476</v>
+        <v>-15.07208404403969</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.938930274944476</v>
       </c>
       <c r="E28">
-        <v>-29.87013136024481</v>
+        <v>-32.7835590766346</v>
       </c>
       <c r="F28">
-        <v>-2.06410395359339</v>
+        <v>-2.308054053542894</v>
       </c>
       <c r="G28">
-        <v>-12.58845981174982</v>
+        <v>-15.07797847037236</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.116173212369647</v>
       </c>
       <c r="E29">
-        <v>-29.62760667052702</v>
+        <v>-37.1687748090723</v>
       </c>
       <c r="F29">
-        <v>-1.847000044469458</v>
+        <v>-2.238086718051737</v>
       </c>
       <c r="G29">
-        <v>-13.44120006339191</v>
+        <v>-16.24169150670035</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.229617992700911</v>
       </c>
       <c r="E30">
-        <v>-29.48365101029719</v>
+        <v>-32.82495838601272</v>
       </c>
       <c r="F30">
-        <v>-2.007510222705161</v>
+        <v>-2.238392373293417</v>
       </c>
       <c r="G30">
-        <v>-14.14740067201093</v>
+        <v>-15.25973404156943</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.271013147257202</v>
       </c>
       <c r="E31">
-        <v>-28.37347296494676</v>
+        <v>-33.88499263867621</v>
       </c>
       <c r="F31">
-        <v>-1.970362816752614</v>
+        <v>-1.914766820591112</v>
       </c>
       <c r="G31">
-        <v>-13.28636584852019</v>
+        <v>-17.02101378991803</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.235681612696819</v>
       </c>
       <c r="E32">
-        <v>-28.63235223854326</v>
+        <v>-32.95536938048561</v>
       </c>
       <c r="F32">
-        <v>-2.164648691046895</v>
+        <v>-1.687380700811189</v>
       </c>
       <c r="G32">
-        <v>-12.63440356274382</v>
+        <v>-14.84938199034015</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.125757786970877</v>
       </c>
       <c r="E33">
-        <v>-29.22942247950657</v>
+        <v>-32.68716145043332</v>
       </c>
       <c r="F33">
-        <v>-2.338552270209469</v>
+        <v>-2.351813431692401</v>
       </c>
       <c r="G33">
-        <v>-13.12797279719376</v>
+        <v>-15.2539356210574</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.948261593491819</v>
       </c>
       <c r="E34">
-        <v>-27.83893189308136</v>
+        <v>-31.47281265324744</v>
       </c>
       <c r="F34">
-        <v>-2.191357891310781</v>
+        <v>-2.76878498660958</v>
       </c>
       <c r="G34">
-        <v>-14.24254740608235</v>
+        <v>-16.09931984051123</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.715211342018868</v>
       </c>
       <c r="E35">
-        <v>-28.17238154816215</v>
+        <v>-32.90200131430521</v>
       </c>
       <c r="F35">
-        <v>-2.263233592430042</v>
+        <v>-2.896472067894844</v>
       </c>
       <c r="G35">
-        <v>-12.66616162610205</v>
+        <v>-15.41093327743902</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.442783496415502</v>
       </c>
       <c r="E36">
-        <v>-27.19164540384698</v>
+        <v>-33.6556209017137</v>
       </c>
       <c r="F36">
-        <v>-1.970785666232036</v>
+        <v>-2.560325736225074</v>
       </c>
       <c r="G36">
-        <v>-13.5545994902941</v>
+        <v>-15.04248114582753</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.145658825267021</v>
       </c>
       <c r="E37">
-        <v>-27.81854470309882</v>
+        <v>-32.02598386718041</v>
       </c>
       <c r="F37">
-        <v>-2.376272185850448</v>
+        <v>-3.21604095789475</v>
       </c>
       <c r="G37">
-        <v>-13.80149832134018</v>
+        <v>-15.25305336067118</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.841181841831446</v>
       </c>
       <c r="E38">
-        <v>-26.81102716350228</v>
+        <v>-32.3620849437927</v>
       </c>
       <c r="F38">
-        <v>-2.664879625203514</v>
+        <v>-2.104316622345271</v>
       </c>
       <c r="G38">
-        <v>-13.33807988038915</v>
+        <v>-14.72434103004911</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.543043734725664</v>
       </c>
       <c r="E39">
-        <v>-25.57582247927408</v>
+        <v>-32.1028456565126</v>
       </c>
       <c r="F39">
-        <v>-2.433209580922327</v>
+        <v>-2.705179397780744</v>
       </c>
       <c r="G39">
-        <v>-13.32722460156588</v>
+        <v>-14.47556511968226</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.263681658314042</v>
       </c>
       <c r="E40">
-        <v>-25.12400304210679</v>
+        <v>-29.26165162901917</v>
       </c>
       <c r="F40">
-        <v>-2.343274089396352</v>
+        <v>-2.770663261825292</v>
       </c>
       <c r="G40">
-        <v>-12.96039960308694</v>
+        <v>-14.26858484674872</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.013237775489539</v>
       </c>
       <c r="E41">
-        <v>-24.58102542316509</v>
+        <v>-28.45175669511736</v>
       </c>
       <c r="F41">
-        <v>-2.862541960509511</v>
+        <v>-2.560980598621109</v>
       </c>
       <c r="G41">
-        <v>-13.99984965732561</v>
+        <v>-15.49509893195668</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.79791138570131</v>
       </c>
       <c r="E42">
-        <v>-24.79985940111175</v>
+        <v>-29.4302874725908</v>
       </c>
       <c r="F42">
-        <v>-2.466442065851909</v>
+        <v>-2.472143407147491</v>
       </c>
       <c r="G42">
-        <v>-12.8630728747779</v>
+        <v>-15.06533549695789</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.625268935325141</v>
       </c>
       <c r="E43">
-        <v>-23.36469994707487</v>
+        <v>-29.51315854693117</v>
       </c>
       <c r="F43">
-        <v>-2.508696923381748</v>
+        <v>-2.734517549864259</v>
       </c>
       <c r="G43">
-        <v>-12.81471904663131</v>
+        <v>-13.85355830521799</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.497993979122639</v>
       </c>
       <c r="E44">
-        <v>-23.27122771508255</v>
+        <v>-29.45110713184107</v>
       </c>
       <c r="F44">
-        <v>-2.560667024849852</v>
+        <v>-2.675682875105684</v>
       </c>
       <c r="G44">
-        <v>-12.66840286543214</v>
+        <v>-14.56579734890064</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.419318859805382</v>
       </c>
       <c r="E45">
-        <v>-24.0118958668291</v>
+        <v>-27.45929633159632</v>
       </c>
       <c r="F45">
-        <v>-2.767678768027646</v>
+        <v>-3.13383711864795</v>
       </c>
       <c r="G45">
-        <v>-13.12008707771922</v>
+        <v>-13.32880704233365</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.38784188779995</v>
       </c>
       <c r="E46">
-        <v>-23.05818112691769</v>
+        <v>-27.55529545208493</v>
       </c>
       <c r="F46">
-        <v>-2.967152862900906</v>
+        <v>-2.422036535688902</v>
       </c>
       <c r="G46">
-        <v>-12.23681366456843</v>
+        <v>-14.0602952530544</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.401453795977047</v>
       </c>
       <c r="E47">
-        <v>-22.75138154137203</v>
+        <v>-29.18680501062039</v>
       </c>
       <c r="F47">
-        <v>-2.647943474143804</v>
+        <v>-3.025079282316977</v>
       </c>
       <c r="G47">
-        <v>-12.79009851945575</v>
+        <v>-14.26837131656144</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.457102688704803</v>
       </c>
       <c r="E48">
-        <v>-21.13062710860479</v>
+        <v>-28.43071287640372</v>
       </c>
       <c r="F48">
-        <v>-3.066821019130215</v>
+        <v>-2.846961461713418</v>
       </c>
       <c r="G48">
-        <v>-12.21835075209592</v>
+        <v>-15.79770927861039</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.553180240166325</v>
       </c>
       <c r="E49">
-        <v>-22.34409058912216</v>
+        <v>-26.7326936201176</v>
       </c>
       <c r="F49">
-        <v>-2.846468929173716</v>
+        <v>-3.286777974460811</v>
       </c>
       <c r="G49">
-        <v>-12.64282228005019</v>
+        <v>-14.21843504764707</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.690222121871302</v>
       </c>
       <c r="E50">
-        <v>-22.24265729982435</v>
+        <v>-26.68825570468033</v>
       </c>
       <c r="F50">
-        <v>-3.298915496596739</v>
+        <v>-3.851140287810193</v>
       </c>
       <c r="G50">
-        <v>-12.8485561325882</v>
+        <v>-15.35955361066953</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.867121664944543</v>
       </c>
       <c r="E51">
-        <v>-20.29549951753224</v>
+        <v>-25.57634778225897</v>
       </c>
       <c r="F51">
-        <v>-3.372939494790294</v>
+        <v>-2.968044489331298</v>
       </c>
       <c r="G51">
-        <v>-12.28540585199386</v>
+        <v>-13.86951016889897</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.086964010776567</v>
       </c>
       <c r="E52">
-        <v>-18.94694260041805</v>
+        <v>-24.19156760155743</v>
       </c>
       <c r="F52">
-        <v>-3.488064620754292</v>
+        <v>-3.568610319907626</v>
       </c>
       <c r="G52">
-        <v>-11.8855515406696</v>
+        <v>-14.40919695798373</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.348860331007389</v>
       </c>
       <c r="E53">
-        <v>-19.73597938304052</v>
+        <v>-24.12746705197885</v>
       </c>
       <c r="F53">
-        <v>-3.300059724120644</v>
+        <v>-3.579512551429512</v>
       </c>
       <c r="G53">
-        <v>-13.58474862852025</v>
+        <v>-13.10704683884003</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.658075575290397</v>
       </c>
       <c r="E54">
-        <v>-19.76098561651088</v>
+        <v>-23.51904845515231</v>
       </c>
       <c r="F54">
-        <v>-3.815768216188853</v>
+        <v>-2.715864661592214</v>
       </c>
       <c r="G54">
-        <v>-13.17830964211838</v>
+        <v>-13.79042620178409</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.014656867217543</v>
       </c>
       <c r="E55">
-        <v>-19.11783815251951</v>
+        <v>-23.94017389549562</v>
       </c>
       <c r="F55">
-        <v>-3.263840369834544</v>
+        <v>-4.090549111047174</v>
       </c>
       <c r="G55">
-        <v>-13.30081637979911</v>
+        <v>-13.30667935594916</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.419065878270709</v>
       </c>
       <c r="E56">
-        <v>-18.08603440681983</v>
+        <v>-23.46689402000597</v>
       </c>
       <c r="F56">
-        <v>-3.661892182032925</v>
+        <v>-3.554179591606142</v>
       </c>
       <c r="G56">
-        <v>-12.91465448482529</v>
+        <v>-13.49313921235753</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.87044571446105</v>
       </c>
       <c r="E57">
-        <v>-17.92091265907815</v>
+        <v>-21.08364871924922</v>
       </c>
       <c r="F57">
-        <v>-3.561363281638575</v>
+        <v>-4.263625995721889</v>
       </c>
       <c r="G57">
-        <v>-12.22185993036755</v>
+        <v>-14.95919609642331</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.359447013743434</v>
       </c>
       <c r="E58">
-        <v>-17.97987339065802</v>
+        <v>-21.2970621138087</v>
       </c>
       <c r="F58">
-        <v>-3.59956385202489</v>
+        <v>-3.690693457811107</v>
       </c>
       <c r="G58">
-        <v>-12.68536610077537</v>
+        <v>-14.46722585546884</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.879678841236517</v>
       </c>
       <c r="E59">
-        <v>-18.06972284344421</v>
+        <v>-22.22672159979136</v>
       </c>
       <c r="F59">
-        <v>-3.304616046039363</v>
+        <v>-4.32033375343603</v>
       </c>
       <c r="G59">
-        <v>-12.97955441957716</v>
+        <v>-14.93029834441102</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.411602630590468</v>
       </c>
       <c r="E60">
-        <v>-16.93585635055966</v>
+        <v>-21.37343029947405</v>
       </c>
       <c r="F60">
-        <v>-3.855358488515966</v>
+        <v>-3.918286251212995</v>
       </c>
       <c r="G60">
-        <v>-12.37475085500771</v>
+        <v>-15.8388659807546</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.936455596161184</v>
       </c>
       <c r="E61">
-        <v>-18.3583587197451</v>
+        <v>-21.80547389064985</v>
       </c>
       <c r="F61">
-        <v>-3.398438743734784</v>
+        <v>-4.3457846993501</v>
       </c>
       <c r="G61">
-        <v>-13.54783107993906</v>
+        <v>-14.58305356752409</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.432802469962745</v>
       </c>
       <c r="E62">
-        <v>-16.09412624438393</v>
+        <v>-19.97296348480993</v>
       </c>
       <c r="F62">
-        <v>-3.405795849564958</v>
+        <v>-4.647656467597928</v>
       </c>
       <c r="G62">
-        <v>-12.30118060148848</v>
+        <v>-15.14967329984359</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.879761712338407</v>
       </c>
       <c r="E63">
-        <v>-14.85015443447688</v>
+        <v>-21.03024895375076</v>
       </c>
       <c r="F63">
-        <v>-3.816864932535295</v>
+        <v>-4.421527810314864</v>
       </c>
       <c r="G63">
-        <v>-13.39927200413704</v>
+        <v>-16.16278961959013</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.26053298021917</v>
       </c>
       <c r="E64">
-        <v>-15.94557418303631</v>
+        <v>-22.4544585576371</v>
       </c>
       <c r="F64">
-        <v>-3.951728577176372</v>
+        <v>-3.861751909296595</v>
       </c>
       <c r="G64">
-        <v>-13.65604784779953</v>
+        <v>-15.37732627439711</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.555880458452807</v>
       </c>
       <c r="E65">
-        <v>-16.13611425538305</v>
+        <v>-21.22030900785269</v>
       </c>
       <c r="F65">
-        <v>-3.896709841821048</v>
+        <v>-3.969761444582523</v>
       </c>
       <c r="G65">
-        <v>-12.66608548355465</v>
+        <v>-15.44747673437427</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.753169727616706</v>
       </c>
       <c r="E66">
-        <v>-14.73388133585594</v>
+        <v>-19.71395288546722</v>
       </c>
       <c r="F66">
-        <v>-4.281906713103807</v>
+        <v>-4.271881854659076</v>
       </c>
       <c r="G66">
-        <v>-13.11467433576251</v>
+        <v>-15.58111683670357</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.843711265862084</v>
       </c>
       <c r="E67">
-        <v>-15.21577436890817</v>
+        <v>-20.9402364759003</v>
       </c>
       <c r="F67">
-        <v>-4.308861387784586</v>
+        <v>-4.579355190729813</v>
       </c>
       <c r="G67">
-        <v>-13.78765361989495</v>
+        <v>-14.52357630636554</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.824475180713885</v>
       </c>
       <c r="E68">
-        <v>-15.99876563873041</v>
+        <v>-20.13755087261871</v>
       </c>
       <c r="F68">
-        <v>-4.399229231025477</v>
+        <v>-4.498282117506637</v>
       </c>
       <c r="G68">
-        <v>-13.09967756446961</v>
+        <v>-14.5225318292479</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.700149415191934</v>
       </c>
       <c r="E69">
-        <v>-16.53768574496123</v>
+        <v>-20.94114217070183</v>
       </c>
       <c r="F69">
-        <v>-4.175978167390767</v>
+        <v>-3.892205782197538</v>
       </c>
       <c r="G69">
-        <v>-13.56338567815533</v>
+        <v>-15.27911231988355</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.478817814758095</v>
       </c>
       <c r="E70">
-        <v>-16.45900350907796</v>
+        <v>-21.55159405235782</v>
       </c>
       <c r="F70">
-        <v>-4.067927455751037</v>
+        <v>-4.082100039988305</v>
       </c>
       <c r="G70">
-        <v>-13.37538972861674</v>
+        <v>-14.36153668912761</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.174775259855755</v>
       </c>
       <c r="E71">
-        <v>-16.27742981526641</v>
+        <v>-20.3885777722859</v>
       </c>
       <c r="F71">
-        <v>-4.365410774907183</v>
+        <v>-4.403993018419118</v>
       </c>
       <c r="G71">
-        <v>-13.10897688688943</v>
+        <v>-14.0082402349949</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.807147517396197</v>
       </c>
       <c r="E72">
-        <v>-15.58868967496582</v>
+        <v>-20.05266915581893</v>
       </c>
       <c r="F72">
-        <v>-4.675821885451061</v>
+        <v>-4.068198269462577</v>
       </c>
       <c r="G72">
-        <v>-13.28059887819079</v>
+        <v>-15.14454029898495</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.393926515296538</v>
       </c>
       <c r="E73">
-        <v>-15.87563190198784</v>
+        <v>-21.11650732664887</v>
       </c>
       <c r="F73">
-        <v>-4.608756691049947</v>
+        <v>-4.834350055733592</v>
       </c>
       <c r="G73">
-        <v>-12.43162602737238</v>
+        <v>-14.40310886473701</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.957651444016982</v>
       </c>
       <c r="E74">
-        <v>-15.45453363248858</v>
+        <v>-20.88083195386768</v>
       </c>
       <c r="F74">
-        <v>-4.476404803990756</v>
+        <v>-4.9773151479851</v>
       </c>
       <c r="G74">
-        <v>-13.10962244326958</v>
+        <v>-13.65142963677225</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.515527311782047</v>
       </c>
       <c r="E75">
-        <v>-16.7811999062497</v>
+        <v>-21.53349827022317</v>
       </c>
       <c r="F75">
-        <v>-4.827362745234673</v>
+        <v>-4.802927746665357</v>
       </c>
       <c r="G75">
-        <v>-13.15912503071831</v>
+        <v>-15.36244702747086</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.082564529894914</v>
       </c>
       <c r="E76">
-        <v>-16.89969648560841</v>
+        <v>-20.65353425800068</v>
       </c>
       <c r="F76">
-        <v>-4.474513067274764</v>
+        <v>-4.652019577394964</v>
       </c>
       <c r="G76">
-        <v>-12.38776460952258</v>
+        <v>-14.83182616734539</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.672458749827527</v>
       </c>
       <c r="E77">
-        <v>-16.54686949024879</v>
+        <v>-20.40260245628765</v>
       </c>
       <c r="F77">
-        <v>-5.001742228024837</v>
+        <v>-5.172485522033153</v>
       </c>
       <c r="G77">
-        <v>-12.1316806698778</v>
+        <v>-13.12551968294917</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.291934952822092</v>
       </c>
       <c r="E78">
-        <v>-18.1893877690969</v>
+        <v>-20.32450892202538</v>
       </c>
       <c r="F78">
-        <v>-4.945903924858273</v>
+        <v>-5.036074596712692</v>
       </c>
       <c r="G78">
-        <v>-12.050095585608</v>
+        <v>-14.5330643298811</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.952799982412589</v>
       </c>
       <c r="E79">
-        <v>-18.04936282430572</v>
+        <v>-21.84615317266075</v>
       </c>
       <c r="F79">
-        <v>-4.864322482036241</v>
+        <v>-5.1706286268473</v>
       </c>
       <c r="G79">
-        <v>-11.63342370294425</v>
+        <v>-14.28733908722869</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.660015837808138</v>
       </c>
       <c r="E80">
-        <v>-19.02042614814052</v>
+        <v>-22.74927127248446</v>
       </c>
       <c r="F80">
-        <v>-4.738316504580217</v>
+        <v>-5.073469852641005</v>
       </c>
       <c r="G80">
-        <v>-11.84380556141939</v>
+        <v>-13.73437701053146</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.421049900274405</v>
       </c>
       <c r="E81">
-        <v>-19.44794579378265</v>
+        <v>-21.35377219380675</v>
       </c>
       <c r="F81">
-        <v>-4.706697815978468</v>
+        <v>-5.304663201441644</v>
       </c>
       <c r="G81">
-        <v>-11.60647586225458</v>
+        <v>-13.92941945625039</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.23997353866133</v>
       </c>
       <c r="E82">
-        <v>-19.56621142096697</v>
+        <v>-23.67107838453782</v>
       </c>
       <c r="F82">
-        <v>-5.183570671588271</v>
+        <v>-5.26586161466042</v>
       </c>
       <c r="G82">
-        <v>-11.6627981735142</v>
+        <v>-12.72854885678962</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.121908399151618</v>
       </c>
       <c r="E83">
-        <v>-19.49391433343451</v>
+        <v>-23.42869181327726</v>
       </c>
       <c r="F83">
-        <v>-5.388533891164444</v>
+        <v>-5.423743632929452</v>
       </c>
       <c r="G83">
-        <v>-11.31535641916769</v>
+        <v>-13.58961678573574</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.072160935882014</v>
       </c>
       <c r="E84">
-        <v>-21.24906028932739</v>
+        <v>-23.70683521530238</v>
       </c>
       <c r="F84">
-        <v>-5.314097337579917</v>
+        <v>-5.32118758896334</v>
       </c>
       <c r="G84">
-        <v>-11.63493993280123</v>
+        <v>-14.03634842189608</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.093355615816672</v>
       </c>
       <c r="E85">
-        <v>-20.63629888592749</v>
+        <v>-26.37229954469116</v>
       </c>
       <c r="F85">
-        <v>-5.573949428626348</v>
+        <v>-4.833299266858698</v>
       </c>
       <c r="G85">
-        <v>-11.74144680389067</v>
+        <v>-14.52495845912819</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.190842243111957</v>
       </c>
       <c r="E86">
-        <v>-23.22064918889088</v>
+        <v>-29.34504347787042</v>
       </c>
       <c r="F86">
-        <v>-5.281568018076791</v>
+        <v>-4.720329564645613</v>
       </c>
       <c r="G86">
-        <v>-11.63625090883479</v>
+        <v>-13.83085789445521</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.364831573848977</v>
       </c>
       <c r="E87">
-        <v>-24.43011402685948</v>
+        <v>-28.33570549172279</v>
       </c>
       <c r="F87">
-        <v>-5.512450168665047</v>
+        <v>-5.242631816292755</v>
       </c>
       <c r="G87">
-        <v>-11.03366872032218</v>
+        <v>-13.4155300932804</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.622369735885314</v>
       </c>
       <c r="E88">
-        <v>-25.1094258842761</v>
+        <v>-27.5400480801011</v>
       </c>
       <c r="F88">
-        <v>-5.453701014025905</v>
+        <v>-6.094389242116933</v>
       </c>
       <c r="G88">
-        <v>-10.94850824686997</v>
+        <v>-12.51059578066616</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.963114301124258</v>
       </c>
       <c r="E89">
-        <v>-26.63133278640392</v>
+        <v>-29.9700747815941</v>
       </c>
       <c r="F89">
-        <v>-6.037462141133505</v>
+        <v>-5.67879076022844</v>
       </c>
       <c r="G89">
-        <v>-11.93575927431819</v>
+        <v>-12.68435969493143</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.394975496546191</v>
       </c>
       <c r="E90">
-        <v>-28.0098138597608</v>
+        <v>-31.27720974696013</v>
       </c>
       <c r="F90">
-        <v>-5.477900832266777</v>
+        <v>-5.673246205818486</v>
       </c>
       <c r="G90">
-        <v>-11.86613188053624</v>
+        <v>-13.43500603268793</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.921658633313132</v>
       </c>
       <c r="E91">
-        <v>-29.85015626139698</v>
+        <v>-31.97950134572868</v>
       </c>
       <c r="F91">
-        <v>-5.807579308977892</v>
+        <v>-5.717865536280078</v>
       </c>
       <c r="G91">
-        <v>-11.26434091240752</v>
+        <v>-12.81901613474128</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.547189954230659</v>
       </c>
       <c r="E92">
-        <v>-29.68240799873085</v>
+        <v>-33.99342015607886</v>
       </c>
       <c r="F92">
-        <v>-5.628651422798585</v>
+        <v>-6.163190970054327</v>
       </c>
       <c r="G92">
-        <v>-11.73292545967258</v>
+        <v>-14.05242774158032</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.279358554579207</v>
       </c>
       <c r="E93">
-        <v>-33.17128702117133</v>
+        <v>-36.08573364421284</v>
       </c>
       <c r="F93">
-        <v>-5.76376925223909</v>
+        <v>-5.908008435899569</v>
       </c>
       <c r="G93">
-        <v>-12.13153500587407</v>
+        <v>-14.7993248865136</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.110371635239273</v>
       </c>
       <c r="E94">
-        <v>-33.67011654701225</v>
+        <v>-35.14262006195339</v>
       </c>
       <c r="F94">
-        <v>-5.611009730753548</v>
+        <v>-6.069020648910466</v>
       </c>
       <c r="G94">
-        <v>-11.87743739355285</v>
+        <v>-12.99398839812838</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.042374683008861</v>
       </c>
       <c r="E95">
-        <v>-34.26497915689684</v>
+        <v>-35.55445760210696</v>
       </c>
       <c r="F95">
-        <v>-5.797115763994583</v>
+        <v>-4.993221890199773</v>
       </c>
       <c r="G95">
-        <v>-12.36211119213877</v>
+        <v>-14.62539213442583</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.064852608069014</v>
       </c>
       <c r="E96">
-        <v>-36.97506254068319</v>
+        <v>-39.72016687820786</v>
       </c>
       <c r="F96">
-        <v>-5.515401404638467</v>
+        <v>-5.261205519269028</v>
       </c>
       <c r="G96">
-        <v>-11.5226164331993</v>
+        <v>-13.40368496134089</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.15218711955773</v>
       </c>
       <c r="E97">
-        <v>-39.08911496829099</v>
+        <v>-41.81280415223338</v>
       </c>
       <c r="F97">
-        <v>-4.991961260291084</v>
+        <v>-5.342350651111357</v>
       </c>
       <c r="G97">
-        <v>-12.32770800289466</v>
+        <v>-14.64096659591533</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.3011197909132</v>
       </c>
       <c r="E98">
-        <v>-42.06186569418125</v>
+        <v>-43.57844258240203</v>
       </c>
       <c r="F98">
-        <v>-5.72613644042346</v>
+        <v>-5.301164003221481</v>
       </c>
       <c r="G98">
-        <v>-12.80386376780804</v>
+        <v>-15.98182857932249</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.44647631562606</v>
       </c>
       <c r="E99">
-        <v>-43.47003997160643</v>
+        <v>-44.95590248487019</v>
       </c>
       <c r="F99">
-        <v>-5.202958399405081</v>
+        <v>-4.827570210709595</v>
       </c>
       <c r="G99">
-        <v>-13.08916658238243</v>
+        <v>-15.28904726704691</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.61218163553273</v>
       </c>
       <c r="E100">
-        <v>-45.67880316884764</v>
+        <v>-47.61031280920624</v>
       </c>
       <c r="F100">
-        <v>-5.348844637217616</v>
+        <v>-4.905190805037114</v>
       </c>
       <c r="G100">
-        <v>-13.7158727162397</v>
+        <v>-15.20293004593385</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.67825105573593</v>
       </c>
       <c r="E101">
-        <v>-47.24911266540644</v>
+        <v>-48.71602917554061</v>
       </c>
       <c r="F101">
-        <v>-5.091579529784055</v>
+        <v>-5.127368116061156</v>
       </c>
       <c r="G101">
-        <v>-13.45390262662609</v>
+        <v>-15.8655291145279</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.75109334745856</v>
       </c>
       <c r="E102">
-        <v>-50.62898112941578</v>
+        <v>-50.83619391094026</v>
       </c>
       <c r="F102">
-        <v>-5.023988545019015</v>
+        <v>-4.61895100602763</v>
       </c>
       <c r="G102">
-        <v>-13.83106976936972</v>
+        <v>-15.999321501952</v>
       </c>
     </row>
   </sheetData>
